--- a/DOM/Energy/A1_Inputs/A-I_Classifier_Modes_Transport.xlsx
+++ b/DOM/Energy/A1_Inputs/A-I_Classifier_Modes_Transport.xlsx
@@ -2662,10 +2662,10 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CCDA0DC61E44874FB77B81A0A8C300E4" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="71904d85c9bd1373b9e56b88e8365113">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9c2c21c4-f980-47d5-be5b-1bb924ee96a2" xmlns:ns3="1b6bb729-2ef5-410d-b4d4-7ced22c361d1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7f50eb003d4f8624802c7eda0096d7ec" ns2:_="" ns3:_="">
-    <xsd:import namespace="9c2c21c4-f980-47d5-be5b-1bb924ee96a2"/>
-    <xsd:import namespace="1b6bb729-2ef5-410d-b4d4-7ced22c361d1"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101000D404091916B8749A73FDE0336A1D2B1" ma:contentTypeVersion="20" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="93002211975624ec5d7eb2d257cf1f9f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="160a8fee-1065-46af-a09f-4bc299cd7729" xmlns:ns3="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f413f3703cea110dc6e6a65a3ede40bd" ns2:_="" ns3:_="">
+    <xsd:import namespace="160a8fee-1065-46af-a09f-4bc299cd7729"/>
+    <xsd:import namespace="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -2674,18 +2674,13 @@
               <xsd:all>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2693,7 +2688,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9c2c21c4-f980-47d5-be5b-1bb924ee96a2" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="160a8fee-1065-46af-a09f-4bc299cd7729" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -2706,91 +2701,52 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:displayName="Etiquetas de imagen_0" ma:hidden="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="13" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="71f7bd95-1200-4052-9a4e-dfdf006e181b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="21" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1b6bb729-2ef5-410d-b4d4-7ced22c361d1" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="14" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="TaxCatchAll" ma:index="12" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{358d400d-8031-419e-a2bc-623ab747dbff}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99">
       <xsd:complexType>
         <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
+          <xsd:extension base="dms:MultiChoiceLookup">
             <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
             </xsd:sequence>
           </xsd:extension>
         </xsd:complexContent>
       </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="15" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -2895,9 +2851,8 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9c2c21c4-f980-47d5-be5b-1bb924ee96a2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="160a8fee-1065-46af-a09f-4bc299cd7729" xsi:nil="true"/>
+    <TaxCatchAll xmlns="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
@@ -2911,7 +2866,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{470559FF-C1A0-44D7-A576-E17A6B1F2F2B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE3C7D59-77F8-407C-B7BE-44D5B48D40E7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
